--- a/26_10/26_10.xlsx
+++ b/26_10/26_10.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\HK2-2024-2025\ĐẠI HỌC\NĂM 3\HK1_2526\MACHINE LEARNING\ML_Pycharm\26_10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B363B2-489F-456A-A430-9D688B2E4F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2999130A-AA09-4745-835A-E00C5E84F07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ex1" sheetId="1" r:id="rId1"/>
+    <sheet name="ex2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$1</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$A$2:$A$11</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$B$1</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$B$2:$B$11</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$C$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$C$2:$C$11</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'ex2'!$B$1</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'ex2'!$B$2:$B$14</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'ex2'!$C$1</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'ex2'!$C$2:$C$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
   <si>
     <t>x</t>
   </si>
@@ -69,7 +68,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,6 +84,17 @@
     </font>
     <font>
       <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
@@ -130,13 +140,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -210,7 +226,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$1</c:f>
+              <c:f>'ex1'!$A$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -233,7 +249,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:f>'ex1'!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -282,7 +298,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
+              <c:f>'ex1'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -305,7 +321,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$11</c:f>
+              <c:f>'ex1'!$B$2:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -354,7 +370,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
+              <c:f>'ex1'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -377,7 +393,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$11</c:f>
+              <c:f>'ex1'!$C$2:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -477,6 +493,7 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1466135584"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -535,6 +552,420 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1466132704"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ex2'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'ex2'!$B$2:$B$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>1.49</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.51</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.54</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.58</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.59</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.62</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.63</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.64</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.66</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.67</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.68</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A95A-4421-B1A3-5BF96688D5FB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ex2'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Y-PREDICTED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'ex2'!$C$2:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>1.4846771919932338</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5014533408514237</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5182294897096138</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5461897378065972</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5741499859035804</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5853340851423738</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.602110234000564</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.6132943332393572</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6300704820975471</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.6412545813363404</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.6580307301945305</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.669214829433324</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.6859909782915139</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A95A-4421-B1A3-5BF96688D5FB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1360302480"/>
+        <c:axId val="1360286160"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1360302480"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1360286160"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1360286160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1360302480"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
@@ -660,6 +1091,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="322">
   <cs:axisTitle>
@@ -1144,6 +1615,522 @@
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -1181,15 +2168,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>2162175</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>7273925</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>6734175</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>473075</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>149225</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1197,6 +2184,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D269756B-9CB1-6CF5-583A-8FF5261FBCD7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>244475</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>549275</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>168275</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F748306-34C5-F5B7-C270-6088C8A8929C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1513,7 +2541,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <f>$E$7+$E$6*A2</f>
+        <f t="shared" ref="C2:C11" si="0">$E$7+$E$6*A2</f>
         <v>0.81818181818181879</v>
       </c>
       <c r="D2" t="s">
@@ -1532,7 +2560,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <f>$E$7+$E$6*A3</f>
+        <f t="shared" si="0"/>
         <v>2.9030303030303033</v>
       </c>
       <c r="D3" t="s">
@@ -1551,7 +2579,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <f>$E$7+$E$6*A4</f>
+        <f t="shared" si="0"/>
         <v>4.9878787878787882</v>
       </c>
       <c r="D4" t="s">
@@ -1570,7 +2598,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <f>$E$7+$E$6*A5</f>
+        <f t="shared" si="0"/>
         <v>7.0727272727272723</v>
       </c>
       <c r="D5" t="s">
@@ -1589,7 +2617,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <f>$E$7+$E$6*A6</f>
+        <f t="shared" si="0"/>
         <v>9.1575757575757564</v>
       </c>
       <c r="D6" t="s">
@@ -1608,7 +2636,7 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <f>$E$7+$E$6*A7</f>
+        <f t="shared" si="0"/>
         <v>11.242424242424242</v>
       </c>
       <c r="D7" t="s">
@@ -1627,7 +2655,7 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <f>$E$7+$E$6*A8</f>
+        <f t="shared" si="0"/>
         <v>13.327272727272726</v>
       </c>
     </row>
@@ -1639,7 +2667,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <f>$E$7+$E$6*A9</f>
+        <f t="shared" si="0"/>
         <v>15.41212121212121</v>
       </c>
     </row>
@@ -1651,7 +2679,7 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <f>$E$7+$E$6*A10</f>
+        <f t="shared" si="0"/>
         <v>17.496969696969696</v>
       </c>
     </row>
@@ -1663,8 +2691,240 @@
         <v>20</v>
       </c>
       <c r="C11">
-        <f>$E$7+$E$6*A11</f>
+        <f t="shared" si="0"/>
         <v>19.581818181818178</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9C5A16-9AAE-455C-A39D-C4D29A3395DA}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="43" customWidth="1"/>
+    <col min="4" max="4" width="16.6328125" customWidth="1"/>
+    <col min="5" max="5" width="37.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="150.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1">
+        <f>STDEV(A2:A14)</f>
+        <v>5.840014488917749</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4">
+        <v>73.5</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1.49</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ref="C2:C14" si="0">$E$7+$E$6*A2</f>
+        <v>1.4846771919932338</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <f>STDEV(B2:B14)</f>
+        <v>6.5496134158769898E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4">
+        <v>75</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="C3">
+        <f t="shared" si="0"/>
+        <v>1.5014533408514237</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <f>AVERAGE(A2:A14)</f>
+        <v>83.192307692307693</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4">
+        <v>76.5</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.51</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>1.5182294897096138</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <f>AVERAGE(B2:B14)</f>
+        <v>1.5930769230769231</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4">
+        <v>79</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.54</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>1.5461897378065972</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <f>CORREL(A2:A14,B2:B14)</f>
+        <v>0.99723903462325769</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4">
+        <v>81.5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1.58</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>1.5741499859035804</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <f>E5*(E2/E1)</f>
+        <v>1.1184099238793339E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4">
+        <v>82.5</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1.59</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>1.5853340851423738</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <f>E4-E6*E3</f>
+        <v>0.66264589794192341</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4">
+        <v>84</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>1.602110234000564</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4">
+        <v>85</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1.62</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>1.6132943332393572</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4">
+        <v>86.5</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1.63</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>1.6300704820975471</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="4">
+        <v>87.5</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1.64</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>1.6412545813363404</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="4">
+        <v>89</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1.66</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>1.6580307301945305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="4">
+        <v>90</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1.67</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>1.669214829433324</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="25.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="4">
+        <v>91.5</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1.68</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>1.6859909782915139</v>
       </c>
     </row>
   </sheetData>

--- a/26_10/26_10.xlsx
+++ b/26_10/26_10.xlsx
@@ -8,20 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\HK2-2024-2025\ĐẠI HỌC\NĂM 3\HK1_2526\MACHINE LEARNING\ML_Pycharm\26_10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2999130A-AA09-4745-835A-E00C5E84F07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B18EAD5-35DD-42A0-974A-CE6E05B7DF75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40680" yWindow="2280" windowWidth="21600" windowHeight="11175" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ex1" sheetId="1" r:id="rId1"/>
     <sheet name="ex2" sheetId="2" r:id="rId2"/>
+    <sheet name="EX3" sheetId="3" r:id="rId3"/>
+    <sheet name="ex4" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'ex2'!$B$1</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'ex2'!$B$2:$B$14</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'ex2'!$C$1</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'ex2'!$C$2:$C$14</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -32,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
   <si>
     <t>x</t>
   </si>
@@ -63,12 +59,69 @@
   <si>
     <t>Y-PREDICTED</t>
   </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>X0</t>
+  </si>
+  <si>
+    <t>x'x</t>
+  </si>
+  <si>
+    <t>(X'x)_inv=</t>
+  </si>
+  <si>
+    <t>(X'Y)=</t>
+  </si>
+  <si>
+    <t>B_hat=</t>
+  </si>
+  <si>
+    <t>predicted price</t>
+  </si>
+  <si>
+    <t>squared error</t>
+  </si>
+  <si>
+    <t>mse=</t>
+  </si>
+  <si>
+    <t>rmse=</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>x0</t>
+  </si>
+  <si>
+    <t>x'y</t>
+  </si>
+  <si>
+    <t>x'x_inv</t>
+  </si>
+  <si>
+    <t>B_hat</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,6 +151,20 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -113,7 +180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -136,11 +203,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
@@ -153,6 +229,27 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2931,4 +3028,1437 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C2F49E2-A3FA-4064-A193-AFE6BD87EC2D}">
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="16" max="16" width="18.453125" customWidth="1"/>
+    <col min="17" max="17" width="21.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="35.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1">
+        <f t="array" ref="K1:M3">MMULT(TRANSPOSE(E2:H12),E2:H12)</f>
+        <v>11</v>
+      </c>
+      <c r="L1">
+        <v>66</v>
+      </c>
+      <c r="M1">
+        <v>47</v>
+      </c>
+      <c r="P1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="6">
+        <v>7</v>
+      </c>
+      <c r="B2" s="6">
+        <v>5</v>
+      </c>
+      <c r="C2" s="6">
+        <v>65</v>
+      </c>
+      <c r="E2" s="8">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6">
+        <v>7</v>
+      </c>
+      <c r="G2" s="6">
+        <v>5</v>
+      </c>
+      <c r="H2" s="6">
+        <v>65</v>
+      </c>
+      <c r="K2" s="9">
+        <v>66</v>
+      </c>
+      <c r="L2">
+        <v>454</v>
+      </c>
+      <c r="M2">
+        <v>261</v>
+      </c>
+      <c r="P2">
+        <f>$N$9+$N$10*F2+$N$11*G2</f>
+        <v>54.810499624828537</v>
+      </c>
+      <c r="Q2">
+        <f>POWER(H2-P2,2)</f>
+        <v>103.82591789561937</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="6">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6">
+        <v>38</v>
+      </c>
+      <c r="E3" s="8">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6">
+        <v>3</v>
+      </c>
+      <c r="G3" s="6">
+        <v>7</v>
+      </c>
+      <c r="H3" s="6">
+        <v>38</v>
+      </c>
+      <c r="K3" s="9">
+        <v>47</v>
+      </c>
+      <c r="L3">
+        <v>261</v>
+      </c>
+      <c r="M3">
+        <v>269</v>
+      </c>
+      <c r="P3">
+        <f t="shared" ref="P3:P12" si="0">$N$9+$N$10*F3+$N$11*G3</f>
+        <v>42.746177132655433</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q12" si="1">POWER(H3-P3,2)</f>
+        <v>22.526197374541344</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="6">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6">
+        <v>51</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6">
+        <v>8</v>
+      </c>
+      <c r="H4" s="6">
+        <v>51</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="0"/>
+        <v>56.295169344614322</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="1"/>
+        <v>28.038818388143273</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="6">
+        <v>8</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6">
+        <v>38</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6">
+        <v>8</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <f t="array" ref="K5:M7">MINVERSE(K1:M3)</f>
+        <v>1.3973194649279432</v>
+      </c>
+      <c r="L5">
+        <v>-0.14197003803461952</v>
+      </c>
+      <c r="M5">
+        <v>-0.10639343838132949</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="0"/>
+        <v>44.672126057595207</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="1"/>
+        <v>44.517266128440966</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="6">
+        <v>9</v>
+      </c>
+      <c r="B6" s="6">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6">
+        <v>55</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
+        <v>9</v>
+      </c>
+      <c r="G6" s="6">
+        <v>3</v>
+      </c>
+      <c r="H6" s="6">
+        <v>55</v>
+      </c>
+      <c r="K6">
+        <v>-0.14197003803461947</v>
+      </c>
+      <c r="L6">
+        <v>1.9405417992703587E-2</v>
+      </c>
+      <c r="M6">
+        <v>5.9768687417527068E-3</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="0"/>
+        <v>57.08424538797891</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="1"/>
+        <v>4.3440788373113586</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="6">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6">
+        <v>4</v>
+      </c>
+      <c r="C7" s="6">
+        <v>43</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6">
+        <v>5</v>
+      </c>
+      <c r="G7" s="6">
+        <v>4</v>
+      </c>
+      <c r="H7" s="6">
+        <v>43</v>
+      </c>
+      <c r="K7">
+        <v>-0.10639343838132957</v>
+      </c>
+      <c r="L7">
+        <v>5.976868741752718E-3</v>
+      </c>
+      <c r="M7">
+        <v>1.6507542239126507E-2</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>41.261507412869634</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="1"/>
+        <v>3.0223564755072347</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="6">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6">
+        <v>25</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>4</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>25</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>21.332557116613586</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="1"/>
+        <v>13.450137302901656</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="6">
+        <v>2</v>
+      </c>
+      <c r="B9" s="6">
+        <v>6</v>
+      </c>
+      <c r="C9" s="6">
+        <v>33</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6">
+        <v>2</v>
+      </c>
+      <c r="G9" s="6">
+        <v>6</v>
+      </c>
+      <c r="H9" s="6">
+        <v>33</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9">
+        <f t="array" ref="K9:K11">MMULT(TRANSPOSE(E2:G12),H2:H12)</f>
+        <v>519</v>
+      </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9">
+        <f t="array" ref="N9:N11">MMULT(K5:M7,K9:K11)</f>
+        <v>1.7514036585681367</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="0"/>
+        <v>34.092473285207895</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="1"/>
+        <v>1.19349787889293</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="6">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6">
+        <v>7</v>
+      </c>
+      <c r="C10" s="6">
+        <v>71</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6">
+        <v>8</v>
+      </c>
+      <c r="G10" s="6">
+        <v>7</v>
+      </c>
+      <c r="H10" s="6">
+        <v>71</v>
+      </c>
+      <c r="K10">
+        <v>3319</v>
+      </c>
+      <c r="N10">
+        <v>4.8952883645113623</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="0"/>
+        <v>67.222618955212241</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="1"/>
+        <v>14.268607557521864</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="6">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6">
+        <v>4</v>
+      </c>
+      <c r="C11" s="6">
+        <v>51</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6">
+        <v>6</v>
+      </c>
+      <c r="G11" s="6">
+        <v>4</v>
+      </c>
+      <c r="H11" s="6">
+        <v>51</v>
+      </c>
+      <c r="K11">
+        <v>2371</v>
+      </c>
+      <c r="N11">
+        <v>3.7584154829361722</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="0"/>
+        <v>46.156795777380999</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="1"/>
+        <v>23.456627141994517</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="6">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6">
+        <v>2</v>
+      </c>
+      <c r="C12" s="6">
+        <v>49</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6">
+        <v>9</v>
+      </c>
+      <c r="G12" s="6">
+        <v>2</v>
+      </c>
+      <c r="H12" s="6">
+        <v>49</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="0"/>
+        <v>53.325829905042738</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="1"/>
+        <v>18.712804367362065</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P13" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q13">
+        <f>AVERAGE(Q2:Q12)</f>
+        <v>25.214209940748784</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="P14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14">
+        <f>SQRT(Q13)</f>
+        <v>5.0213753037139917</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7031F485-DDA1-4CE2-8F7F-5EFE5F320815}">
+  <dimension ref="A1:T23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="19" max="19" width="18.54296875" customWidth="1"/>
+    <col min="20" max="20" width="17.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1">
+        <f t="array" ref="M1:P4">MMULT(TRANSPOSE(F2:J21),F2:J21)</f>
+        <v>20</v>
+      </c>
+      <c r="N1">
+        <v>50.840000000000018</v>
+      </c>
+      <c r="O1">
+        <v>435.64000000000004</v>
+      </c>
+      <c r="P1">
+        <v>11.029999999999998</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A2" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="B2" s="11">
+        <v>7.01</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0.94</v>
+      </c>
+      <c r="D2" s="11">
+        <v>33.520000000000003</v>
+      </c>
+      <c r="F2" s="11">
+        <v>1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="H2" s="11">
+        <v>7.01</v>
+      </c>
+      <c r="I2" s="11">
+        <v>0.94</v>
+      </c>
+      <c r="J2" s="11">
+        <v>33.520000000000003</v>
+      </c>
+      <c r="M2">
+        <v>50.840000000000018</v>
+      </c>
+      <c r="N2">
+        <v>228.6694</v>
+      </c>
+      <c r="O2">
+        <v>991.42410000000007</v>
+      </c>
+      <c r="P2">
+        <v>26.494299999999999</v>
+      </c>
+      <c r="S2">
+        <f>$Q$11+$Q$12*G2+$Q$13*H2+$Q$14*I2</f>
+        <v>35.128368193795353</v>
+      </c>
+      <c r="T2">
+        <f>POWER(J2-S2,2)</f>
+        <v>2.5868482468125165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A3" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="B3" s="11">
+        <v>14.45</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.84</v>
+      </c>
+      <c r="D3" s="11">
+        <v>42.89</v>
+      </c>
+      <c r="F3" s="11">
+        <v>1</v>
+      </c>
+      <c r="G3" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="H3" s="11">
+        <v>14.45</v>
+      </c>
+      <c r="I3" s="11">
+        <v>0.84</v>
+      </c>
+      <c r="J3" s="11">
+        <v>42.89</v>
+      </c>
+      <c r="M3">
+        <v>435.64000000000004</v>
+      </c>
+      <c r="N3">
+        <v>991.42410000000007</v>
+      </c>
+      <c r="O3">
+        <v>15643.789200000001</v>
+      </c>
+      <c r="P3">
+        <v>222.99350000000001</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:S21" si="0">$Q$11+$Q$12*G3+$Q$13*H3+$Q$14*I3</f>
+        <v>26.623780513896161</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T21" si="1">POWER(J3-S3,2)</f>
+        <v>264.58989637010427</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A4" s="11">
+        <v>5.71</v>
+      </c>
+      <c r="B4" s="11">
+        <v>42.28</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="D4" s="11">
+        <v>12.04</v>
+      </c>
+      <c r="F4" s="11">
+        <v>1</v>
+      </c>
+      <c r="G4" s="11">
+        <v>5.71</v>
+      </c>
+      <c r="H4" s="11">
+        <v>42.28</v>
+      </c>
+      <c r="I4" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="J4" s="11">
+        <v>12.04</v>
+      </c>
+      <c r="M4">
+        <v>11.029999999999998</v>
+      </c>
+      <c r="N4">
+        <v>26.494299999999999</v>
+      </c>
+      <c r="O4">
+        <v>222.99350000000001</v>
+      </c>
+      <c r="P4">
+        <v>7.5643000000000002</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="0"/>
+        <v>19.383050772711986</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="1"/>
+        <v>53.920394650626108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A5" s="11">
+        <v>3.58</v>
+      </c>
+      <c r="B5" s="11">
+        <v>11.13</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.24</v>
+      </c>
+      <c r="D5" s="11">
+        <v>6.91</v>
+      </c>
+      <c r="F5" s="11">
+        <v>1</v>
+      </c>
+      <c r="G5" s="11">
+        <v>3.58</v>
+      </c>
+      <c r="H5" s="11">
+        <v>11.13</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0.24</v>
+      </c>
+      <c r="J5" s="11">
+        <v>6.91</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="0"/>
+        <v>18.424979688737992</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="1"/>
+        <v>132.59475723204849</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A6" s="11">
+        <v>0.45</v>
+      </c>
+      <c r="B6" s="11">
+        <v>3</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="D6" s="11">
+        <v>6.57</v>
+      </c>
+      <c r="F6" s="11">
+        <v>1</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0.45</v>
+      </c>
+      <c r="H6" s="11">
+        <v>3</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="J6" s="11">
+        <v>6.57</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6">
+        <f t="array" ref="M6:P9">MINVERSE(M1:P4)</f>
+        <v>0.53744317176876155</v>
+      </c>
+      <c r="N6">
+        <v>-3.9569552520799127E-2</v>
+      </c>
+      <c r="O6">
+        <v>-5.6285940092465183E-3</v>
+      </c>
+      <c r="P6">
+        <v>-0.47915745158927026</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="0"/>
+        <v>28.765037999149943</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="1"/>
+        <v>492.61971178370987</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A7" s="11">
+        <v>0.13</v>
+      </c>
+      <c r="B7" s="11">
+        <v>63.46</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0.18</v>
+      </c>
+      <c r="D7" s="11">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="F7" s="11">
+        <v>1</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0.13</v>
+      </c>
+      <c r="H7" s="11">
+        <v>63.46</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0.18</v>
+      </c>
+      <c r="J7" s="11">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="M7">
+        <v>-3.9569552520799148E-2</v>
+      </c>
+      <c r="N7">
+        <v>1.0547374926949125E-2</v>
+      </c>
+      <c r="O7">
+        <v>2.373361311408064E-4</v>
+      </c>
+      <c r="P7">
+        <v>1.3759691474134927E-2</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="0"/>
+        <v>14.073769025806541</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="1"/>
+        <v>144.09047082491253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A8" s="11">
+        <v>1</v>
+      </c>
+      <c r="B8" s="11">
+        <v>48.25</v>
+      </c>
+      <c r="C8" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="D8" s="11">
+        <v>4.18</v>
+      </c>
+      <c r="F8" s="11">
+        <v>1</v>
+      </c>
+      <c r="G8" s="11">
+        <v>1</v>
+      </c>
+      <c r="H8" s="11">
+        <v>48.25</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="J8" s="11">
+        <v>4.18</v>
+      </c>
+      <c r="M8">
+        <v>-5.6285940092465157E-3</v>
+      </c>
+      <c r="N8">
+        <v>2.3733613114080621E-4</v>
+      </c>
+      <c r="O8">
+        <v>1.733085255858903E-4</v>
+      </c>
+      <c r="P8">
+        <v>2.2670521479142762E-3</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="0"/>
+        <v>18.053081476286145</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="1"/>
+        <v>192.46238964767377</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A9" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="B9" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="C9" s="11">
+        <v>0.34</v>
+      </c>
+      <c r="D9" s="11">
+        <v>58.45</v>
+      </c>
+      <c r="F9" s="11">
+        <v>1</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="H9" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0.34</v>
+      </c>
+      <c r="J9" s="11">
+        <v>58.45</v>
+      </c>
+      <c r="M9">
+        <v>-0.47915745158927031</v>
+      </c>
+      <c r="N9">
+        <v>1.3759691474134913E-2</v>
+      </c>
+      <c r="O9">
+        <v>2.2670521479142788E-3</v>
+      </c>
+      <c r="P9">
+        <v>0.71586470711904004</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="0"/>
+        <v>22.263443002407584</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="1"/>
+        <v>1309.4669073400048</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A10" s="11">
+        <v>7.56</v>
+      </c>
+      <c r="B10" s="11">
+        <v>13.85</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D10" s="11">
+        <v>29.64</v>
+      </c>
+      <c r="F10" s="11">
+        <v>1</v>
+      </c>
+      <c r="G10" s="11">
+        <v>7.56</v>
+      </c>
+      <c r="H10" s="11">
+        <v>13.85</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J10" s="11">
+        <v>29.64</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="0"/>
+        <v>16.660205844107288</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="1"/>
+        <v>168.47505632934661</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A11" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="B11" s="11">
+        <v>50.46</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0.43</v>
+      </c>
+      <c r="D11" s="11">
+        <v>48.87</v>
+      </c>
+      <c r="F11" s="11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="H11" s="11">
+        <v>50.46</v>
+      </c>
+      <c r="I11" s="11">
+        <v>0.43</v>
+      </c>
+      <c r="J11" s="11">
+        <v>48.87</v>
+      </c>
+      <c r="L11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11">
+        <f t="array" ref="M11:M14">MMULT(TRANSPOSE(F2:I21),J2:J21)</f>
+        <v>467.71999999999997</v>
+      </c>
+      <c r="P11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q11">
+        <f t="array" ref="Q11:Q14">MMULT(M6:P9,M11:M14)</f>
+        <v>22.126545009326577</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="0"/>
+        <v>19.373960597828784</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="1"/>
+        <v>870.01634041443674</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A12" s="11">
+        <v>0.42</v>
+      </c>
+      <c r="B12" s="11">
+        <v>3.1</v>
+      </c>
+      <c r="C12" s="11">
+        <v>0.94</v>
+      </c>
+      <c r="D12" s="11">
+        <v>33.75</v>
+      </c>
+      <c r="F12" s="11">
+        <v>1</v>
+      </c>
+      <c r="G12" s="11">
+        <v>0.42</v>
+      </c>
+      <c r="H12" s="11">
+        <v>3.1</v>
+      </c>
+      <c r="I12" s="11">
+        <v>0.94</v>
+      </c>
+      <c r="J12" s="11">
+        <v>33.75</v>
+      </c>
+      <c r="M12">
+        <v>1023.8301000000001</v>
+      </c>
+      <c r="Q12">
+        <v>-1.6043410177634763</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="0"/>
+        <v>36.339010132621425</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="1"/>
+        <v>6.7029734668164087</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A13" s="11">
+        <v>2.93</v>
+      </c>
+      <c r="B13" s="11">
+        <v>11.21</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0.53</v>
+      </c>
+      <c r="D13" s="11">
+        <v>0.04</v>
+      </c>
+      <c r="F13" s="11">
+        <v>1</v>
+      </c>
+      <c r="G13" s="11">
+        <v>2.93</v>
+      </c>
+      <c r="H13" s="11">
+        <v>11.21</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0.53</v>
+      </c>
+      <c r="J13" s="11">
+        <v>0.04</v>
+      </c>
+      <c r="M13">
+        <v>9043.8549000000003</v>
+      </c>
+      <c r="Q13">
+        <v>-0.17011917974078983</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="0"/>
+        <v>24.20946922474123</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="1"/>
+        <v>584.16324260571355</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A14" s="11">
+        <v>5.64</v>
+      </c>
+      <c r="B14" s="11">
+        <v>18.11</v>
+      </c>
+      <c r="C14" s="11">
+        <v>0.09</v>
+      </c>
+      <c r="D14" s="11">
+        <v>16.75</v>
+      </c>
+      <c r="F14" s="11">
+        <v>1</v>
+      </c>
+      <c r="G14" s="11">
+        <v>5.64</v>
+      </c>
+      <c r="H14" s="11">
+        <v>18.11</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0.09</v>
+      </c>
+      <c r="J14" s="11">
+        <v>16.75</v>
+      </c>
+      <c r="M14">
+        <v>287.65010000000001</v>
+      </c>
+      <c r="Q14">
+        <v>16.397508306331872</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="0"/>
+        <v>11.472979071604737</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="1"/>
+        <v>27.846949878721606</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A15" s="11">
+        <v>3.93</v>
+      </c>
+      <c r="B15" s="11">
+        <v>21.56</v>
+      </c>
+      <c r="C15" s="11">
+        <v>0.43</v>
+      </c>
+      <c r="D15" s="11">
+        <v>4.63</v>
+      </c>
+      <c r="F15" s="11">
+        <v>1</v>
+      </c>
+      <c r="G15" s="11">
+        <v>3.93</v>
+      </c>
+      <c r="H15" s="11">
+        <v>21.56</v>
+      </c>
+      <c r="I15" s="11">
+        <v>0.43</v>
+      </c>
+      <c r="J15" s="11">
+        <v>4.63</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="0"/>
+        <v>19.204643866027389</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="1"/>
+        <v>212.42024382152982</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A16" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="B16" s="11">
+        <v>11.2</v>
+      </c>
+      <c r="C16" s="11">
+        <v>0.79</v>
+      </c>
+      <c r="D16" s="11">
+        <v>61.69</v>
+      </c>
+      <c r="F16" s="11">
+        <v>1</v>
+      </c>
+      <c r="G16" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H16" s="11">
+        <v>11.2</v>
+      </c>
+      <c r="I16" s="11">
+        <v>0.79</v>
+      </c>
+      <c r="J16" s="11">
+        <v>61.69</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="0"/>
+        <v>32.373071249350176</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="1"/>
+        <v>859.48231137067819</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A17" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="B17" s="11">
+        <v>7.62</v>
+      </c>
+      <c r="C17" s="11">
+        <v>0.33</v>
+      </c>
+      <c r="D17" s="11">
+        <v>24.55</v>
+      </c>
+      <c r="F17" s="11">
+        <v>1</v>
+      </c>
+      <c r="G17" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="H17" s="11">
+        <v>7.62</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0.33</v>
+      </c>
+      <c r="J17" s="11">
+        <v>24.55</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="0"/>
+        <v>25.920546397238581</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="1"/>
+        <v>1.8783974269836536</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A18" s="11">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="B18" s="11">
+        <v>22.54</v>
+      </c>
+      <c r="C18" s="11">
+        <v>0.94</v>
+      </c>
+      <c r="D18" s="11">
+        <v>32.9</v>
+      </c>
+      <c r="F18" s="11">
+        <v>1</v>
+      </c>
+      <c r="G18" s="11">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="H18" s="11">
+        <v>22.54</v>
+      </c>
+      <c r="I18" s="11">
+        <v>0.94</v>
+      </c>
+      <c r="J18" s="11">
+        <v>32.9</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="0"/>
+        <v>31.956984796558942</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="1"/>
+        <v>0.88927767392097778</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A19" s="11">
+        <v>1.95</v>
+      </c>
+      <c r="B19" s="11">
+        <v>44.38</v>
+      </c>
+      <c r="C19" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="D19" s="11">
+        <v>9.23</v>
+      </c>
+      <c r="F19" s="11">
+        <v>1</v>
+      </c>
+      <c r="G19" s="11">
+        <v>1.95</v>
+      </c>
+      <c r="H19" s="11">
+        <v>44.38</v>
+      </c>
+      <c r="I19" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="J19" s="11">
+        <v>9.23</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="0"/>
+        <v>26.205948303490231</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="1"/>
+        <v>288.18282080277282</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A20" s="11">
+        <v>3.81</v>
+      </c>
+      <c r="B20" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="C20" s="11">
+        <v>0.61</v>
+      </c>
+      <c r="D20" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="F20" s="11">
+        <v>1</v>
+      </c>
+      <c r="G20" s="11">
+        <v>3.81</v>
+      </c>
+      <c r="H20" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="I20" s="11">
+        <v>0.61</v>
+      </c>
+      <c r="J20" s="11">
+        <v>11.4</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="0"/>
+        <v>25.080830309935827</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="1"/>
+        <v>187.1651179692588</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A21" s="11">
+        <v>5.41</v>
+      </c>
+      <c r="B21" s="11">
+        <v>11.73</v>
+      </c>
+      <c r="C21" s="11">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="D21" s="11">
+        <v>27.64</v>
+      </c>
+      <c r="F21" s="11">
+        <v>1</v>
+      </c>
+      <c r="G21" s="11">
+        <v>5.41</v>
+      </c>
+      <c r="H21" s="11">
+        <v>11.73</v>
+      </c>
+      <c r="I21" s="11">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J21" s="11">
+        <v>27.64</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="0"/>
+        <v>16.206839533702947</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="1"/>
+        <v>130.71715824809786</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S22" t="s">
+        <v>20</v>
+      </c>
+      <c r="T22">
+        <f>AVERAGE(T2:T21)</f>
+        <v>296.51356330520844</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S23" t="s">
+        <v>21</v>
+      </c>
+      <c r="T23">
+        <f>SQRT(T22)</f>
+        <v>17.219569196272257</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>